--- a/artfynd/A 59362-2024 artfynd.xlsx
+++ b/artfynd/A 59362-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67733181</v>
+        <v>67733122</v>
       </c>
       <c r="B2" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,45 +686,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sjöborgen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474294.7983013326</v>
+        <v>474342</v>
       </c>
       <c r="R2" t="n">
-        <v>6324133.218866621</v>
+        <v>6324353</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,19 +753,9 @@
           <t>2017-09-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-09-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,6 +764,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -788,6 +773,11 @@
           <t>barrskog</t>
         </is>
       </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>gränlåga</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -800,6 +790,119 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>67733181</v>
+      </c>
+      <c r="B3" t="n">
+        <v>96348</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sjöborgen, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>474295</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6324133</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Moheda</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2017-09-27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2017-09-27</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Per Darell</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Per Darell</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59362-2024 artfynd.xlsx
+++ b/artfynd/A 59362-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67733122</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,8 +913,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67733181</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>